--- a/tracking_forms/011_gymnastics_skills_checklist--tracking_forms.xlsx
+++ b/tracking_forms/011_gymnastics_skills_checklist--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gymnastics_skills_checklist_1</t>
+          <t>skill_1_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Skills 1</t>
+          <t>Backhand Stand</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skill_1_1</t>
+          <t>skill_1_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Backhand Stand</t>
+          <t>Kip Cartwheel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>skill_1_2</t>
+          <t>skill_1_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kip Cartwheel</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>skill_1_3</t>
+          <t>skill_2_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Handspring</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>skill_2_1</t>
+          <t>skill_2_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Handspring</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>skill_2_2</t>
+          <t>skill_2_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>skill_2_2</t>
+          <t>skill_3_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Handstand</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>skill_2_3</t>
+          <t>skill_3_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Handstand</t>
+          <t>Round Off</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>skill_3_1</t>
+          <t>skill_4_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>skill_3_2</t>
+          <t>skill_4_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -738,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>skill_3_3</t>
+          <t>skill_5_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Side</t>
+          <t>Kip</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>skill_4_1</t>
+          <t>skill_6_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Handstand</t>
+          <t>Skill 6 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>skill_4_2</t>
+          <t>skill_7_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Round Off</t>
+          <t>Backward</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>skill_4_3</t>
+          <t>skill_8_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Skill 8 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>skill_5_1</t>
+          <t>skill_9_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Skill 9 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>skill_6_1</t>
+          <t>skill_10_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Skill 10 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>skill_7_1</t>
+          <t>skill_11_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Backhand Stand</t>
+          <t>Skill 11 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>skill_8_1</t>
+          <t>skill_12_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kip</t>
+          <t>Skill 12 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>skill_9_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Handspring</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>skill_10_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Cartwheel</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>skill_11_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Backward</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>skill_12_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>skill_13_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Dis</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>skill_14_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Side</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>skill_15_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1369,97 +1208,97 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>skill_2_2_choices</t>
+          <t>skill_2_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>skill_2_2_choices</t>
+          <t>skill_2_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>skill_2_2_choices</t>
+          <t>skill_2_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>skill_2_2_choices</t>
+          <t>skill_2_1_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>skill_2_2_choices</t>
+          <t>skill_2_1_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1497,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1514,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1531,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1548,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1565,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1582,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1599,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1616,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1794,1287 +1633,862 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>skill_3_3_choices</t>
+          <t>skill_4_1_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>skill_3_3_choices</t>
+          <t>skill_4_1_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>skill_3_3_choices</t>
+          <t>skill_4_1_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>skill_3_3_choices</t>
+          <t>skill_4_1_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>skill_3_3_choices</t>
+          <t>skill_4_1_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>skill_4_1_choices</t>
+          <t>skill_4_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>skill_4_1_choices</t>
+          <t>skill_4_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>skill_4_1_choices</t>
+          <t>skill_4_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>skill_4_1_choices</t>
+          <t>skill_4_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>skill_4_1_choices</t>
+          <t>skill_4_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>skill_4_2_choices</t>
+          <t>skill_5_1_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>skill_4_2_choices</t>
+          <t>skill_5_1_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>skill_4_2_choices</t>
+          <t>skill_5_1_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>skill_4_2_choices</t>
+          <t>skill_5_1_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>skill_4_2_choices</t>
+          <t>skill_5_1_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>skill_4_3_choices</t>
+          <t>skill_6_1_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>skill_4_3_choices</t>
+          <t>skill_6_1_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>skill_4_3_choices</t>
+          <t>skill_6_1_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>skill_4_3_choices</t>
+          <t>skill_6_1_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>skill_4_3_choices</t>
+          <t>skill_6_1_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>skill_5_1_choices</t>
+          <t>skill_7_1_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>skill_5_1_choices</t>
+          <t>skill_7_1_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>skill_5_1_choices</t>
+          <t>skill_7_1_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>skill_5_1_choices</t>
+          <t>skill_7_1_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>skill_5_1_choices</t>
+          <t>skill_7_1_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>skill_6_1_choices</t>
+          <t>skill_8_1_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>skill_6_1_choices</t>
+          <t>skill_8_1_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>skill_6_1_choices</t>
+          <t>skill_8_1_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>skill_6_1_choices</t>
+          <t>skill_8_1_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>skill_6_1_choices</t>
+          <t>skill_8_1_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>skill_7_1_choices</t>
+          <t>skill_9_1_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>skill_7_1_choices</t>
+          <t>skill_9_1_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>skill_7_1_choices</t>
+          <t>skill_9_1_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>skill_7_1_choices</t>
+          <t>skill_9_1_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>skill_7_1_choices</t>
+          <t>skill_9_1_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>skill_8_1_choices</t>
+          <t>skill_10_1_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>skill_8_1_choices</t>
+          <t>skill_10_1_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>skill_8_1_choices</t>
+          <t>skill_10_1_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>skill_8_1_choices</t>
+          <t>skill_10_1_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>skill_8_1_choices</t>
+          <t>skill_10_1_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>skill_9_1_choices</t>
+          <t>skill_11_1_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>skill_9_1_choices</t>
+          <t>skill_11_1_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>skill_9_1_choices</t>
+          <t>skill_11_1_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>skill_9_1_choices</t>
+          <t>skill_11_1_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>skill_9_1_choices</t>
+          <t>skill_11_1_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>skill_10_1_choices</t>
+          <t>skill_12_1_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>skill_10_1_choices</t>
+          <t>skill_12_1_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>skill_10_1_choices</t>
+          <t>skill_12_1_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>skill_10_1_choices</t>
+          <t>skill_12_1_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>skill_10_1_choices</t>
+          <t>skill_12_1_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
+          <t>mastered</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>skill_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'none'}</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>skill_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>skill_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>skill_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>skill_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>skill_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'none'}</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>skill_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>skill_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>skill_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>skill_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>skill_13_1_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'none'}</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>skill_13_1_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>skill_13_1_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>skill_13_1_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>skill_13_1_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>skill_14_1_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'none'}</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>skill_14_1_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>skill_14_1_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>skill_14_1_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>skill_14_1_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>skill_15_1_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'none'}</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>skill_15_1_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'basic'}</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Basic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>skill_15_1_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'proficient'}</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Proficient'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>skill_15_1_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'advanced'}</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Advanced'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>skill_15_1_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>{'value':_41,_'label':_'mastered'}</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>{'value': 41, 'label': 'Mastered'}</t>
+          <t>Mastered</t>
         </is>
       </c>
     </row>
